--- a/artfynd/A 16534-2025 artfynd.xlsx
+++ b/artfynd/A 16534-2025 artfynd.xlsx
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115512151</v>
+        <v>115512140</v>
       </c>
       <c r="B2" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346219</v>
+        <v>346160</v>
       </c>
       <c r="R2" t="n">
-        <v>6434682</v>
+        <v>6434684</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,61 +768,57 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115512140</v>
+        <v>115512146</v>
       </c>
       <c r="B3" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -889,34 +880,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115512146</v>
+        <v>115512151</v>
       </c>
       <c r="B4" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346160</v>
+        <v>346219</v>
       </c>
       <c r="R4" t="n">
-        <v>6434684</v>
+        <v>6434682</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,12 +997,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 16534-2025 artfynd.xlsx
+++ b/artfynd/A 16534-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115512140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115512146</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,8 +1021,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115512151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>